--- a/reference/CA_Baseline_Summary_-_Mirage.xlsx
+++ b/reference/CA_Baseline_Summary_-_Mirage.xlsx
@@ -778,7 +778,7 @@
       </c>
       <c r="G3" s="8" t="inlineStr">
         <is>
-          <t>AC_ExcludedFromCA, BG_BreakGlass, AC_ServiceAccount, All Guest/External</t>
+          <t>CA_ExcludedFromCA, BG_BreakGlass, CA_ServiceAccount, All Guest/External</t>
         </is>
       </c>
       <c r="H3" s="8" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="G4" s="8" t="inlineStr">
         <is>
-          <t>AC_ExcludedFromCA, BG_BreakGlass, AC_ServiceAccount, All Guest/External</t>
+          <t>CA_ExcludedFromCA, BG_BreakGlass, CA_ServiceAccount, All Guest/External</t>
         </is>
       </c>
       <c r="H4" s="8" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="G5" s="8" t="inlineStr">
         <is>
-          <t>AC_ExcludedFromCA, BG_BreakGlass, AC_ServiceAccount, All Guest/External</t>
+          <t>CA_ExcludedFromCA, BG_BreakGlass, CA_ServiceAccount, All Guest/External</t>
         </is>
       </c>
       <c r="H5" s="8" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>AC_ExcludedFromCA, BG_BreakGlass, AC_ServiceAccount, All Guest/External</t>
+          <t>CA_ExcludedFromCA, BG_BreakGlass, CA_ServiceAccount, All Guest/External</t>
         </is>
       </c>
       <c r="H6" s="8" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>AC_ExcludedFromCA, BG_BreakGlass, AC_ServiceAccount, All Guest/External</t>
+          <t>CA_ExcludedFromCA, BG_BreakGlass, CA_ServiceAccount, All Guest/External</t>
         </is>
       </c>
       <c r="H7" s="8" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="G8" s="8" t="inlineStr">
         <is>
-          <t>AC_ExcludedFromCA, BG_BreakGlass, AC_ServiceAccount, All Guest/External, AC_TravelException</t>
+          <t>CA_ExcludedFromCA, BG_BreakGlass, CA_ServiceAccount, All Guest/External, CA_TravelException</t>
         </is>
       </c>
       <c r="H8" s="8" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="G9" s="8" t="inlineStr">
         <is>
-          <t>AC_ExcludedFromCA, BG_BreakGlass, AC_ServiceAccount, All Guest/External</t>
+          <t>CA_ExcludedFromCA, BG_BreakGlass, CA_ServiceAccount, All Guest/External</t>
         </is>
       </c>
       <c r="H9" s="8" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
-          <t>AC_ExcludedFromCA, BG_BreakGlass, AC_ServiceAccount, All Guest/External, AC_DeviceCodeApproved</t>
+          <t>CA_ExcludedFromCA, BG_BreakGlass, CA_ServiceAccount, All Guest/External, CA_DeviceCodeApproved</t>
         </is>
       </c>
       <c r="H10" s="8" t="inlineStr">
@@ -1277,7 +1277,7 @@
       </c>
       <c r="G11" s="8" t="inlineStr">
         <is>
-          <t>AC_ExcludedFromCA, BG_BreakGlass, AC_ServiceAccount, All Guest/External</t>
+          <t>CA_ExcludedFromCA, BG_BreakGlass, CA_ServiceAccount, All Guest/External</t>
         </is>
       </c>
       <c r="H11" s="8" t="inlineStr">
@@ -1339,7 +1339,7 @@
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
-          <t>AC_ExcludedFromCA, BG_BreakGlass, AC_ServiceAccount, All Guest/External</t>
+          <t>CA_ExcludedFromCA, BG_BreakGlass, CA_ServiceAccount, All Guest/External</t>
         </is>
       </c>
       <c r="H12" s="8" t="inlineStr">
@@ -1401,7 +1401,7 @@
       </c>
       <c r="G13" s="8" t="inlineStr">
         <is>
-          <t>AC_ExcludedFromCA, BG_BreakGlass, AC_ServiceAccount, All Guest/External</t>
+          <t>CA_ExcludedFromCA, BG_BreakGlass, CA_ServiceAccount, All Guest/External</t>
         </is>
       </c>
       <c r="H13" s="8" t="inlineStr">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="G14" s="8" t="inlineStr">
         <is>
-          <t>AC_ExcludedFromCA, BG_BreakGlass, AC_ServiceAccount, All Guest/External, AUTOPILOT_DevicePrep</t>
+          <t>CA_ExcludedFromCA, BG_BreakGlass, CA_ServiceAccount, All Guest/External, AUTOPILOT_DevicePrep</t>
         </is>
       </c>
       <c r="H14" s="8" t="inlineStr">
@@ -1520,12 +1520,12 @@
       </c>
       <c r="F15" s="8" t="inlineStr">
         <is>
-          <t>AC_TokenProtection_Pilot</t>
+          <t>CA_TokenProtection_Pilot</t>
         </is>
       </c>
       <c r="G15" s="8" t="inlineStr">
         <is>
-          <t>AC_ExcludedFromCA, BG_BreakGlass</t>
+          <t>CA_ExcludedFromCA, BG_BreakGlass</t>
         </is>
       </c>
       <c r="H15" s="8" t="inlineStr">
@@ -1587,7 +1587,7 @@
       </c>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>AC_ExcludedFromCA, BG_BreakGlass, AC_ServiceAccount, All Guest/External</t>
+          <t>CA_ExcludedFromCA, BG_BreakGlass, CA_ServiceAccount, All Guest/External</t>
         </is>
       </c>
       <c r="H16" s="8" t="inlineStr">
@@ -1649,7 +1649,7 @@
       </c>
       <c r="G17" s="8" t="inlineStr">
         <is>
-          <t>AC_ExcludedFromCA, BG_BreakGlass, AC_ServiceAccount, All Guest/External, AUTOPILOT_DevicePrep</t>
+          <t>CA_ExcludedFromCA, BG_BreakGlass, CA_ServiceAccount, All Guest/External, AUTOPILOT_DevicePrep</t>
         </is>
       </c>
       <c r="H17" s="8" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="G18" s="8" t="inlineStr">
         <is>
-          <t>AC_ExcludedFromCA, BG_BreakGlass, AC_ServiceAccount, All Guest/External</t>
+          <t>CA_ExcludedFromCA, BG_BreakGlass, CA_ServiceAccount, All Guest/External</t>
         </is>
       </c>
       <c r="H18" s="8" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="G19" s="8" t="inlineStr">
         <is>
-          <t>AC_ExcludedFromCA, BG_BreakGlass, AC_ServiceAccount, All Guest/External</t>
+          <t>CA_ExcludedFromCA, BG_BreakGlass, CA_ServiceAccount, All Guest/External</t>
         </is>
       </c>
       <c r="H19" s="8" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="G20" s="8" t="inlineStr">
         <is>
-          <t>AC_ExcludedFromCA, BG_BreakGlass, AC_ServiceAccount, All Guest/External</t>
+          <t>CA_ExcludedFromCA, BG_BreakGlass, CA_ServiceAccount, All Guest/External</t>
         </is>
       </c>
       <c r="H20" s="8" t="inlineStr">
@@ -1897,7 +1897,7 @@
       </c>
       <c r="G21" s="8" t="inlineStr">
         <is>
-          <t>AC_ExcludedFromCA, BG_BreakGlass, AC_ServiceAccount, All Guest/External</t>
+          <t>CA_ExcludedFromCA, BG_BreakGlass, CA_ServiceAccount, All Guest/External</t>
         </is>
       </c>
       <c r="H21" s="8" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="G22" s="8" t="inlineStr">
         <is>
-          <t>AC_ExcludedFromCA, BG_BreakGlass, AC_ServiceAccount, All Guest/External</t>
+          <t>CA_ExcludedFromCA, BG_BreakGlass, CA_ServiceAccount, All Guest/External</t>
         </is>
       </c>
       <c r="H22" s="8" t="inlineStr">
@@ -2021,7 +2021,7 @@
       </c>
       <c r="G23" s="8" t="inlineStr">
         <is>
-          <t>AC_ExcludedFromCA, BG_BreakGlass, AC_ServiceAccount</t>
+          <t>CA_ExcludedFromCA, BG_BreakGlass, CA_ServiceAccount</t>
         </is>
       </c>
       <c r="H23" s="8" t="inlineStr">
@@ -2083,7 +2083,7 @@
       </c>
       <c r="G24" s="8" t="inlineStr">
         <is>
-          <t>AC_ExcludedFromCA, BG_BreakGlass, AC_ServiceAccount</t>
+          <t>CA_ExcludedFromCA, BG_BreakGlass, CA_ServiceAccount</t>
         </is>
       </c>
       <c r="H24" s="8" t="inlineStr">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="G25" s="8" t="inlineStr">
         <is>
-          <t>AC_ExcludedFromCA, BG_BreakGlass, AC_ServiceAccount</t>
+          <t>CA_ExcludedFromCA, BG_BreakGlass, CA_ServiceAccount</t>
         </is>
       </c>
       <c r="H25" s="8" t="inlineStr">
@@ -2208,7 +2208,7 @@
       </c>
       <c r="G26" s="8" t="inlineStr">
         <is>
-          <t>AC_ExcludedFromCA, BG_BreakGlass, AC_ServiceAccount</t>
+          <t>CA_ExcludedFromCA, BG_BreakGlass, CA_ServiceAccount</t>
         </is>
       </c>
       <c r="H26" s="8" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="G27" s="8" t="inlineStr">
         <is>
-          <t>AC_ExcludedFromCA, BG_BreakGlass, AC_ServiceAccount</t>
+          <t>CA_ExcludedFromCA, BG_BreakGlass, CA_ServiceAccount</t>
         </is>
       </c>
       <c r="H27" s="8" t="inlineStr">
@@ -2332,7 +2332,7 @@
       </c>
       <c r="G28" s="8" t="inlineStr">
         <is>
-          <t>AC_ExcludedFromCA, BG_BreakGlass, AC_ServiceAccount</t>
+          <t>CA_ExcludedFromCA, BG_BreakGlass, CA_ServiceAccount</t>
         </is>
       </c>
       <c r="H28" s="8" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="G29" s="8" t="inlineStr">
         <is>
-          <t>AC_ExcludedFromCA, BG_BreakGlass, AC_ServiceAccount, All Guest/External</t>
+          <t>CA_ExcludedFromCA, BG_BreakGlass, CA_ServiceAccount, All Guest/External</t>
         </is>
       </c>
       <c r="H29" s="8" t="inlineStr">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G30" s="8" t="inlineStr">
         <is>
-          <t>AC_ExcludedFromCA, BG_BreakGlass, AC_ServiceAccount, All Guest/External</t>
+          <t>CA_ExcludedFromCA, BG_BreakGlass, CA_ServiceAccount, All Guest/External</t>
         </is>
       </c>
       <c r="H30" s="8" t="inlineStr">
@@ -2513,12 +2513,12 @@
       </c>
       <c r="F31" s="8" t="inlineStr">
         <is>
-          <t>AC_ServiceAccount_Interactive</t>
+          <t>CA_ServiceAccount_Interactive</t>
         </is>
       </c>
       <c r="G31" s="8" t="inlineStr">
         <is>
-          <t>AC_ExcludedFromCA, BG_BreakGlass, AC_ServiceAccount_NonInteractive</t>
+          <t>CA_ExcludedFromCA, BG_BreakGlass, CA_ServiceAccount_NonInteractive</t>
         </is>
       </c>
       <c r="H31" s="8" t="inlineStr">
@@ -2575,12 +2575,12 @@
       </c>
       <c r="F32" s="8" t="inlineStr">
         <is>
-          <t>AC_ServiceAccount</t>
+          <t>CA_ServiceAccount</t>
         </is>
       </c>
       <c r="G32" s="8" t="inlineStr">
         <is>
-          <t>AC_ExcludedFromCA, BG_BreakGlass</t>
+          <t>CA_ExcludedFromCA, BG_BreakGlass</t>
         </is>
       </c>
       <c r="H32" s="8" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="F33" s="8" t="inlineStr">
         <is>
-          <t>AC_ServiceAccount</t>
+          <t>CA_ServiceAccount</t>
         </is>
       </c>
       <c r="G33" s="8" t="inlineStr">
         <is>
-          <t>AC_ExcludedFromCA, BG_BreakGlass</t>
+          <t>CA_ExcludedFromCA, BG_BreakGlass</t>
         </is>
       </c>
       <c r="H33" s="8" t="inlineStr">
@@ -2700,12 +2700,12 @@
       </c>
       <c r="F34" s="8" t="inlineStr">
         <is>
-          <t>AC_ServiceAccount</t>
+          <t>CA_ServiceAccount</t>
         </is>
       </c>
       <c r="G34" s="8" t="inlineStr">
         <is>
-          <t>AC_ExcludedFromCA, BG_BreakGlass</t>
+          <t>CA_ExcludedFromCA, BG_BreakGlass</t>
         </is>
       </c>
       <c r="H34" s="8" t="inlineStr">
@@ -2768,7 +2768,7 @@
       </c>
       <c r="G35" s="8" t="inlineStr">
         <is>
-          <t>AC_ExcludedFromCA, BG_BreakGlass</t>
+          <t>CA_ExcludedFromCA, BG_BreakGlass</t>
         </is>
       </c>
       <c r="H35" s="8" t="inlineStr">
@@ -2830,7 +2830,7 @@
       </c>
       <c r="G36" s="8" t="inlineStr">
         <is>
-          <t>AC_ExcludedFromCA, BG_BreakGlass</t>
+          <t>CA_ExcludedFromCA, BG_BreakGlass</t>
         </is>
       </c>
       <c r="H36" s="8" t="inlineStr">
@@ -2892,7 +2892,7 @@
       </c>
       <c r="G37" s="8" t="inlineStr">
         <is>
-          <t>AC_ExcludedFromCA, BG_BreakGlass</t>
+          <t>CA_ExcludedFromCA, BG_BreakGlass</t>
         </is>
       </c>
       <c r="H37" s="8" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="G38" s="8" t="inlineStr">
         <is>
-          <t>AC_ExcludedFromCA, BG_BreakGlass</t>
+          <t>CA_ExcludedFromCA, BG_BreakGlass</t>
         </is>
       </c>
       <c r="H38" s="8" t="inlineStr">
@@ -3017,7 +3017,7 @@
       </c>
       <c r="G39" s="8" t="inlineStr">
         <is>
-          <t>AC_ExcludedFromCA, BG_BreakGlass, AC_MSP_PartnerUsers (per-tenant)</t>
+          <t>CA_ExcludedFromCA, BG_BreakGlass, CA_MSP_PartnerUsers (per-tenant)</t>
         </is>
       </c>
       <c r="H39" s="8" t="inlineStr">
@@ -3080,7 +3080,7 @@
       </c>
       <c r="G40" s="8" t="inlineStr">
         <is>
-          <t>AC_ExcludedFromCA, BG_BreakGlass</t>
+          <t>CA_ExcludedFromCA, BG_BreakGlass</t>
         </is>
       </c>
       <c r="H40" s="8" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="G41" s="8" t="inlineStr">
         <is>
-          <t>AC_ExcludedFromCA, BG_BreakGlass</t>
+          <t>CA_ExcludedFromCA, BG_BreakGlass</t>
         </is>
       </c>
       <c r="H41" s="8" t="inlineStr">
@@ -3205,7 +3205,7 @@
       </c>
       <c r="G42" s="8" t="inlineStr">
         <is>
-          <t>AC_ExcludedFromCA, AC_ExcludedAgents</t>
+          <t>CA_ExcludedFromCA, CA_ExcludedAgents</t>
         </is>
       </c>
       <c r="H42" s="8" t="inlineStr">
